--- a/output/pdf_financials_xlsx/LFNT.xlsx
+++ b/output/pdf_financials_xlsx/LFNT.xlsx
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.043058</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.00105</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.058405</v>
+        <v>0.101463</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.002872</v>
+        <v>-0.001822</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.0183</v>
@@ -4080,7 +4080,11 @@
           <t>Prepaids and deposit -</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4500,7 +4504,11 @@
           <t>Prepaids and deposit</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.043058</v>
       </c>

--- a/output/pdf_financials_xlsx/LFNT.xlsx
+++ b/output/pdf_financials_xlsx/LFNT.xlsx
@@ -619,7 +619,7 @@
         <v>0.241659</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.166839</v>
+        <v>0.151481</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         <v>-0.241659</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.166839</v>
+        <v>-0.151481</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000196</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
         <v>-0.325076</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.8936539999999999</v>
+        <v>-0.89385</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.151688</v>
@@ -1029,7 +1029,7 @@
         <v>-0.325076</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.8936539999999999</v>
+        <v>-0.89385</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.151688</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.460771</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.185486</v>
       </c>
     </row>
     <row r="35">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.460771</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.185486</v>
       </c>
     </row>
     <row r="37">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.461821</v>
+        <v>0.00105</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.185486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>-0.241659</v>
+        <v>0.241659</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.151481</v>
+        <v>0.151481</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">

--- a/output/pdf_financials_xlsx/LFNT.xlsx
+++ b/output/pdf_financials_xlsx/LFNT.xlsx
@@ -1822,18 +1822,14 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0.073035</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0.07170899999999999</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.048634</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
@@ -1891,18 +1887,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.018673</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0.014071</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.011355</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -2670,7 +2662,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.007734</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0.000646</v>
@@ -2775,7 +2767,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.101463</v>
+        <v>0.09372900000000001</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.001822</v>
@@ -4946,7 +4938,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>-0.007734</v>
       </c>
@@ -4980,7 +4976,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.25</v>
       </c>
